--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132007</v>
+        <v>122132097</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>79748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563757</v>
+        <v>563795</v>
       </c>
       <c r="R2" t="n">
-        <v>7111146</v>
+        <v>7111091</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132097</v>
+        <v>122132007</v>
       </c>
       <c r="B3" t="n">
-        <v>79741</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563795</v>
+        <v>563757</v>
       </c>
       <c r="R3" t="n">
-        <v>7111091</v>
+        <v>7111146</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>122132207</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>56573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>122132090</v>
       </c>
       <c r="B5" t="n">
-        <v>79741</v>
+        <v>79748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132207</v>
+        <v>122132097</v>
       </c>
       <c r="B2" t="n">
-        <v>56576</v>
+        <v>79754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563922</v>
+        <v>563795</v>
       </c>
       <c r="R2" t="n">
-        <v>7110892</v>
+        <v>7111091</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132097</v>
+        <v>122132090</v>
       </c>
       <c r="B3" t="n">
         <v>79754</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563795</v>
+        <v>563876</v>
       </c>
       <c r="R3" t="n">
-        <v>7111091</v>
+        <v>7110966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132090</v>
+        <v>122132007</v>
       </c>
       <c r="B4" t="n">
-        <v>79754</v>
+        <v>90744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563876</v>
+        <v>563757</v>
       </c>
       <c r="R4" t="n">
-        <v>7110966</v>
+        <v>7111146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132007</v>
+        <v>122132207</v>
       </c>
       <c r="B5" t="n">
-        <v>90744</v>
+        <v>56576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563757</v>
+        <v>563922</v>
       </c>
       <c r="R5" t="n">
-        <v>7111146</v>
+        <v>7110892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132097</v>
+        <v>122132207</v>
       </c>
       <c r="B2" t="n">
-        <v>79754</v>
+        <v>56576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563795</v>
+        <v>563922</v>
       </c>
       <c r="R2" t="n">
-        <v>7111091</v>
+        <v>7110892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132090</v>
+        <v>122132007</v>
       </c>
       <c r="B3" t="n">
-        <v>79754</v>
+        <v>90754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563876</v>
+        <v>563757</v>
       </c>
       <c r="R3" t="n">
-        <v>7110966</v>
+        <v>7111146</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132007</v>
+        <v>122132090</v>
       </c>
       <c r="B4" t="n">
-        <v>90744</v>
+        <v>79755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563757</v>
+        <v>563876</v>
       </c>
       <c r="R4" t="n">
-        <v>7111146</v>
+        <v>7110966</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132207</v>
+        <v>122132097</v>
       </c>
       <c r="B5" t="n">
-        <v>56576</v>
+        <v>79755</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563922</v>
+        <v>563795</v>
       </c>
       <c r="R5" t="n">
-        <v>7110892</v>
+        <v>7111091</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132207</v>
+        <v>122132090</v>
       </c>
       <c r="B2" t="n">
-        <v>56576</v>
+        <v>79755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563922</v>
+        <v>563876</v>
       </c>
       <c r="R2" t="n">
-        <v>7110892</v>
+        <v>7110966</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132007</v>
+        <v>122132097</v>
       </c>
       <c r="B3" t="n">
-        <v>90754</v>
+        <v>79755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563757</v>
+        <v>563795</v>
       </c>
       <c r="R3" t="n">
-        <v>7111146</v>
+        <v>7111091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132090</v>
+        <v>122132207</v>
       </c>
       <c r="B4" t="n">
-        <v>79755</v>
+        <v>56576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563876</v>
+        <v>563922</v>
       </c>
       <c r="R4" t="n">
-        <v>7110966</v>
+        <v>7110892</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132097</v>
+        <v>122132007</v>
       </c>
       <c r="B5" t="n">
-        <v>79755</v>
+        <v>90754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563795</v>
+        <v>563757</v>
       </c>
       <c r="R5" t="n">
-        <v>7111091</v>
+        <v>7111146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132090</v>
+        <v>122132097</v>
       </c>
       <c r="B2" t="n">
-        <v>79755</v>
+        <v>79760</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563876</v>
+        <v>563795</v>
       </c>
       <c r="R2" t="n">
-        <v>7110966</v>
+        <v>7111091</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132097</v>
+        <v>122132207</v>
       </c>
       <c r="B3" t="n">
-        <v>79755</v>
+        <v>56581</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563795</v>
+        <v>563922</v>
       </c>
       <c r="R3" t="n">
-        <v>7111091</v>
+        <v>7110892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132207</v>
+        <v>122132007</v>
       </c>
       <c r="B4" t="n">
-        <v>56576</v>
+        <v>90766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563922</v>
+        <v>563757</v>
       </c>
       <c r="R4" t="n">
-        <v>7110892</v>
+        <v>7111146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132007</v>
+        <v>122132090</v>
       </c>
       <c r="B5" t="n">
-        <v>90754</v>
+        <v>79760</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563757</v>
+        <v>563876</v>
       </c>
       <c r="R5" t="n">
-        <v>7111146</v>
+        <v>7110966</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132097</v>
+        <v>122132007</v>
       </c>
       <c r="B2" t="n">
-        <v>79760</v>
+        <v>90773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563795</v>
+        <v>563757</v>
       </c>
       <c r="R2" t="n">
-        <v>7111091</v>
+        <v>7111146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132207</v>
+        <v>122132090</v>
       </c>
       <c r="B3" t="n">
-        <v>56581</v>
+        <v>79760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563922</v>
+        <v>563876</v>
       </c>
       <c r="R3" t="n">
-        <v>7110892</v>
+        <v>7110966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132007</v>
+        <v>122132207</v>
       </c>
       <c r="B4" t="n">
-        <v>90766</v>
+        <v>56581</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563757</v>
+        <v>563922</v>
       </c>
       <c r="R4" t="n">
-        <v>7111146</v>
+        <v>7110892</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132090</v>
+        <v>122132097</v>
       </c>
       <c r="B5" t="n">
         <v>79760</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563876</v>
+        <v>563795</v>
       </c>
       <c r="R5" t="n">
-        <v>7110966</v>
+        <v>7111091</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132007</v>
+        <v>122132097</v>
       </c>
       <c r="B2" t="n">
-        <v>90773</v>
+        <v>79761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6461</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563757</v>
+        <v>563795</v>
       </c>
       <c r="R2" t="n">
-        <v>7111146</v>
+        <v>7111091</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132090</v>
+        <v>122132207</v>
       </c>
       <c r="B3" t="n">
-        <v>79760</v>
+        <v>56581</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +784,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
+        <v>102612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563876</v>
+        <v>563922</v>
       </c>
       <c r="R3" t="n">
-        <v>7110966</v>
+        <v>7110892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132207</v>
+        <v>122132007</v>
       </c>
       <c r="B4" t="n">
-        <v>56581</v>
+        <v>90778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +881,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563922</v>
+        <v>563757</v>
       </c>
       <c r="R4" t="n">
-        <v>7110892</v>
+        <v>7111146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132097</v>
+        <v>122132090</v>
       </c>
       <c r="B5" t="n">
-        <v>79760</v>
+        <v>79761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,11 +984,6 @@
       <c r="E5" t="n">
         <v>6461</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Nephroma arcticum</t>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563795</v>
+        <v>563876</v>
       </c>
       <c r="R5" t="n">
-        <v>7111091</v>
+        <v>7110966</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122132097</v>
       </c>
       <c r="B2" t="n">
-        <v>79761</v>
+        <v>79765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>6461</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -775,7 +780,7 @@
         <v>122132207</v>
       </c>
       <c r="B3" t="n">
-        <v>56581</v>
+        <v>56585</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>102612</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -872,7 +882,7 @@
         <v>122132007</v>
       </c>
       <c r="B4" t="n">
-        <v>90778</v>
+        <v>90791</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -886,6 +896,11 @@
       </c>
       <c r="E4" t="n">
         <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -969,7 +984,7 @@
         <v>122132090</v>
       </c>
       <c r="B5" t="n">
-        <v>79761</v>
+        <v>79765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -983,6 +998,11 @@
       </c>
       <c r="E5" t="n">
         <v>6461</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 15861-2024 artfynd.xlsx
+++ b/artfynd/A 15861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132097</v>
+        <v>122132207</v>
       </c>
       <c r="B2" t="n">
-        <v>79765</v>
+        <v>56585</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563795</v>
+        <v>563922</v>
       </c>
       <c r="R2" t="n">
-        <v>7111091</v>
+        <v>7110892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132207</v>
+        <v>122132097</v>
       </c>
       <c r="B3" t="n">
-        <v>56585</v>
+        <v>79765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563922</v>
+        <v>563795</v>
       </c>
       <c r="R3" t="n">
-        <v>7110892</v>
+        <v>7111091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>122132007</v>
       </c>
       <c r="B4" t="n">
-        <v>90791</v>
+        <v>90804</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
